--- a/Server/Functions/Data/ServerChartData.xlsx
+++ b/Server/Functions/Data/ServerChartData.xlsx
@@ -4,13 +4,21 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="4"/>
   </bookViews>
   <sheets>
-    <sheet name="MapReward" sheetId="15" r:id="rId1"/>
-    <sheet name="GachaInfo" sheetId="16" r:id="rId2"/>
-    <sheet name="Gacha_Equipment" sheetId="17" r:id="rId3"/>
-    <sheet name="Equipment" sheetId="18" r:id="rId4"/>
+    <sheet name="GachaInfo" sheetId="16" r:id="rId1"/>
+    <sheet name="Gacha_Equipment" sheetId="17" r:id="rId2"/>
+    <sheet name="Equipment" sheetId="18" r:id="rId3"/>
+    <sheet name="Dungeon" sheetId="19" r:id="rId4"/>
+    <sheet name="DungeonReward" sheetId="20" r:id="rId5"/>
+    <sheet name="RewardItem" sheetId="21" r:id="rId6"/>
+    <sheet name="Reward_Equipment" sheetId="22" r:id="rId7"/>
+    <sheet name="Reward_Material" sheetId="23" r:id="rId8"/>
+    <sheet name="Reward_CardSkill" sheetId="24" r:id="rId9"/>
+    <sheet name="Reward_Currency" sheetId="25" r:id="rId10"/>
+    <sheet name="Material" sheetId="26" r:id="rId11"/>
+    <sheet name="CardSkill" sheetId="27" r:id="rId12"/>
   </sheets>
   <calcPr calcId="145621"/>
   <extLst>
@@ -33,14 +41,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="64">
   <si>
     <t>GachaType</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>CurrencyType</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -57,23 +65,23 @@
       </rPr>
       <t>urrencyCost</t>
     </r>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Equipment</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Gold</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Dia</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Skill</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -90,7 +98,7 @@
       </rPr>
       <t>achaID</t>
     </r>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -107,7 +115,7 @@
       </rPr>
       <t>rade</t>
     </r>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -124,71 +132,269 @@
       </rPr>
       <t>eight</t>
     </r>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Normal</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Magic</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Rare</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Epic</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Legendary</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>EquipmentType</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Weapon</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Armor</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Accessory</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>ItemID</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>GachaID</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>MapID</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>RewardExp</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>DungeonID</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>10001;20001;30001;40001</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>10002;50001;60001</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>RewardType</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>RewardSourceID</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equipment</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Material</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Currency</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>RewardItemID</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>EquipmentSourceID</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>G</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>rade</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>W</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>eight</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Normal</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Magic</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rare</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Epic</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Legendary</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reward_EquipmentID</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaterialSourceID</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaterialGrade</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reward_MaterialID</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>CardSkillSourceID</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>CardGrade</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Uncommon</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mythic</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reward_CardSkillID</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>CurrencySourceID</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>CurrencyType</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>MinCount</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxCount</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gold</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dia</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reward_CurrencyID</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Exp</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ExtraExp</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaterialID</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>CardSkillID</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>DungeonRewardID</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>DungeonID</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>StageRollRewardIDs</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>StageFixRewardIDs</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>10001;20001;30001;40001</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -254,12 +460,12 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -267,10 +473,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -547,60 +768,13 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="10.875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>3000</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -681,13 +855,280 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D2" s="1">
+        <v>3000</v>
+      </c>
+      <c r="E2" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1">
+        <v>2</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3" s="7">
+        <v>100</v>
+      </c>
+      <c r="E3" s="1">
+        <v>300</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>10001</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>10002</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>10003</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>10004</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>10005</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>20002</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>30003</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>30004</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>40001</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="8">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="8">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="8">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="9">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="9">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="9">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="9">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="9">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -797,12 +1238,12 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C56"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -1429,7 +1870,791 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5" customWidth="1"/>
+    <col min="3" max="3" width="11.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
+        <v>500</v>
+      </c>
+      <c r="C2" s="1">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C3" s="1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1">
+        <v>1500</v>
+      </c>
+      <c r="C4" s="1">
+        <v>750</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
+        <v>1</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" s="5">
+        <v>50001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="5">
+        <v>50001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1">
+        <v>1</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="5">
+        <v>50001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1">
+        <v>1</v>
+      </c>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1">
+        <v>2</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="5">
+        <v>50001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1">
+        <v>2</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="5">
+        <v>50001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1">
+        <v>2</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="5">
+        <v>50001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1">
+        <v>2</v>
+      </c>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1">
+        <v>3</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="5">
+        <v>50001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1">
+        <v>3</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="5">
+        <v>50001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1">
+        <v>3</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="5">
+        <v>50001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1">
+        <v>3</v>
+      </c>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>10001</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>10002</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>20001</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>30001</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>40001</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>40002</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>50001</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>60001</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="1">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="20.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" s="1">
+        <v>660000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1">
+        <v>1</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" s="1">
+        <v>280000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1">
+        <v>1</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="1">
+        <v>59000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1">
+        <v>1</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1">
+        <v>2</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="1">
+        <v>648900</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1">
+        <v>2</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="1">
+        <v>350000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1">
+        <v>2</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1">
+        <v>2</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" s="1">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" s="1">
+        <v>659900</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1">
+        <v>1</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" s="1">
+        <v>280000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1">
+        <v>1</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="1">
+        <v>59000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1">
+        <v>1</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1">
+        <v>1</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1">
+        <v>2</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="1">
+        <v>800000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1">
+        <v>2</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="1">
+        <v>200000</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D2" s="1">
+        <v>660000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1">
+        <v>1</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="1">
+        <v>280000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1">
+        <v>1</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="1">
+        <v>59000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1">
+        <v>1</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1">
+        <v>2</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="1">
+        <v>648900</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1">
+        <v>2</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" s="1">
+        <v>350000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1">
+        <v>2</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1">
+        <v>2</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="1">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>